--- a/Школы.xlsx
+++ b/Школы.xlsx
@@ -509,15 +509,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C1:D540"/>
+  <dimension ref="C4:D540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95.42578125" customWidth="1" min="3" max="3"/>
     <col width="26.140625" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
     <row r="3" ht="15.75" customHeight="1" thickBot="1"/>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="C4" s="1" t="n"/>
@@ -4870,9 +4868,24 @@
           <t>Агинский округ</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>26-001</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>МБОУ 'АМСОШ'</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>26-001-001</t>
         </is>
       </c>
     </row>
@@ -4885,9 +4898,24 @@
           <t>Агинский округ</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>26-001</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>МОУ 'НСОШ'</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>26-001-002</t>
         </is>
       </c>
     </row>
@@ -4900,9 +4928,24 @@
           <t>Акшинский округ</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>26-002</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>МБОУ'СОШ с. Акша'</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>26-002-001</t>
         </is>
       </c>
     </row>
@@ -4915,9 +4958,24 @@
           <t>Александрово-Заводский округ</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>26-003</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>МОУ Александрово-Заводская СОШ</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>26-003-001</t>
         </is>
       </c>
     </row>
@@ -4930,9 +4988,24 @@
           <t>Балейский округ</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>26-004</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>МКОУ 'СОШ №5'</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>26-004-001</t>
         </is>
       </c>
     </row>
@@ -4945,9 +5018,24 @@
           <t>Балейский округ</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>26-004</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>МКОУ 'Ундино-Посельская СОШ'</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>26-004-002</t>
         </is>
       </c>
     </row>
@@ -4960,9 +5048,24 @@
           <t>Борзинский район</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>26-005</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>МОУ СОШ №43</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>26-005-001</t>
         </is>
       </c>
     </row>
@@ -4975,9 +5078,24 @@
           <t>Борзинский район</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>26-005</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Школа №47</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>26-005-002</t>
         </is>
       </c>
     </row>
@@ -4990,9 +5108,24 @@
           <t>Газимуро-Заводский округ</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>26-006</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>МОУ Газимуро-Заводская СОШ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>26-006-001</t>
         </is>
       </c>
     </row>
@@ -5005,9 +5138,24 @@
           <t>ГО 'Город Чита'</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>26-007</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>МБОУ 'Гимназия № 21'</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>26-007-001</t>
         </is>
       </c>
     </row>
@@ -5020,9 +5168,24 @@
           <t>ГО 'Город Чита'</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>26-007</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>МБОУ 'Средняя общеобразовательная школа № 22'</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>26-007-002</t>
         </is>
       </c>
     </row>
@@ -5035,9 +5198,24 @@
           <t>ГО 'Город Чита'</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>26-007</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>МБОУ 'Средняя общеобразовательная школа № 40'</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>26-007-003</t>
         </is>
       </c>
     </row>
@@ -5050,9 +5228,24 @@
           <t>ГО 'Город Чита'</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>26-007</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>МБОУ «Средняя общеобразовательная школа № 47»</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>26-007-004</t>
         </is>
       </c>
     </row>
@@ -5065,9 +5258,24 @@
           <t>ГО 'Город Чита'</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>26-007</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>МБОУ «Средняя общеобразовательная школа № 49'</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>26-007-005</t>
         </is>
       </c>
     </row>
@@ -5080,9 +5288,24 @@
           <t>ГО 'Город Чита'</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>26-007</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>МБОУ «Средняя общеобразовательная школа № 9»</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>26-007-006</t>
         </is>
       </c>
     </row>
@@ -5095,9 +5318,24 @@
           <t>ГО 'ЗАТО п. Горный'</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>26-008</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>МОУ 'СОШ № 1' городского округа ЗАТО п. Горный</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>26-008-001</t>
         </is>
       </c>
     </row>
@@ -5110,9 +5348,24 @@
           <t>ГО «Поселок Агинское»</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>26-009</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>МАОУ 'АСОШ № 1'</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>26-009-001</t>
         </is>
       </c>
     </row>
@@ -5125,9 +5378,24 @@
           <t>Дульдургинский округ</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>26-010</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>МАОУ 'Дульдургинская СОШ №2'</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>26-010-001</t>
         </is>
       </c>
     </row>
@@ -5140,9 +5408,24 @@
           <t>Дульдургинский округ</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>26-010</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>МБОУ 'Дульдургинская СОШ'</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>26-010-002</t>
         </is>
       </c>
     </row>
@@ -5155,9 +5438,24 @@
           <t>Забайкальский район</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>26-011</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>МАОУ СОШ № 1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>26-011-001</t>
         </is>
       </c>
     </row>
@@ -5170,9 +5468,24 @@
           <t>Каларский округ</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>26-012</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>МОУ Новочарская СОШ № 2</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>26-012-001</t>
         </is>
       </c>
     </row>
@@ -5185,9 +5498,24 @@
           <t>Калганский район</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>26-013</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>МОУ СОШ с. Калга</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>26-013-001</t>
         </is>
       </c>
     </row>
@@ -5200,9 +5528,24 @@
           <t>Карымский округ</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>26-014</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>МОУ 'СОШ № 2 П.КАРЫМСКОЕ'</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>26-014-001</t>
         </is>
       </c>
     </row>
@@ -5215,9 +5558,24 @@
           <t>Карымский округ</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>26-014</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>МОУ 'СОШ № 3 П.ДАРАСУН'</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>26-014-002</t>
         </is>
       </c>
     </row>
@@ -5230,9 +5588,24 @@
           <t>Краснокаменский округ</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>26-015</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>МАОУ 'СОШ № 1'</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>26-015-001</t>
         </is>
       </c>
     </row>
@@ -5245,9 +5618,24 @@
           <t>Краснокаменский округ</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>26-015</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>МАОУ 'СОШ № 6'</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>26-015-002</t>
         </is>
       </c>
     </row>
@@ -5260,9 +5648,24 @@
           <t>Красночикойский район</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>26-016</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>МОУ Красночикойская СОШ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>26-016-001</t>
         </is>
       </c>
     </row>
@@ -5275,9 +5678,24 @@
           <t>Красночикойский район</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>26-016</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>МОУ Красночикойская СОШ № 2</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>26-016-002</t>
         </is>
       </c>
     </row>
@@ -5290,9 +5708,24 @@
           <t>Кыринский район</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>26-017</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>МБОУ ' Мангутская СОШ '</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>26-017-001</t>
         </is>
       </c>
     </row>
@@ -5305,9 +5738,24 @@
           <t>Кыринский район</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>26-017</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>МБОУ 'Кыринская СОШ'</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>26-017-002</t>
         </is>
       </c>
     </row>
@@ -5320,9 +5768,24 @@
           <t>Могойтуйский округ</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>26-018</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>МАОУ 'МСОШ№3'</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>26-018-001</t>
         </is>
       </c>
     </row>
@@ -5335,9 +5798,24 @@
           <t>Могойтуйский округ</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>26-018</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>МОУ 'МСОШ№2 им. Ю.Б.Шагдарова'</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>26-018-002</t>
         </is>
       </c>
     </row>
@@ -5350,9 +5828,24 @@
           <t>Могочинский район</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>26-019</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>МОУ СОШ № 1 г. Могоча</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>26-019-001</t>
         </is>
       </c>
     </row>
@@ -5365,9 +5858,24 @@
           <t>Могочинский район</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>26-019</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>МОУ СОШ № 92 г. Могоча</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>26-019-002</t>
         </is>
       </c>
     </row>
@@ -5380,9 +5888,24 @@
           <t>Нерчинский район</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>26-020</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>МАОУ СОШ № 9 г. Нерчинск</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>26-020-001</t>
         </is>
       </c>
     </row>
@@ -5395,9 +5918,24 @@
           <t>Нерчинский район</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>26-020</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>МБОУ 'СОКШ с. Знаменка'</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>26-020-002</t>
         </is>
       </c>
     </row>
@@ -5410,9 +5948,24 @@
           <t>Нерчинский район</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>26-020</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>МБОУ СОШ № 1 г. Нерчинска</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>26-020-003</t>
         </is>
       </c>
     </row>
@@ -5425,9 +5978,24 @@
           <t>Нерчинско-Заводский округ</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>26-021</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>МОУ Михайловская СОШ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>26-021-001</t>
         </is>
       </c>
     </row>
@@ -5440,9 +6008,24 @@
           <t>Нерчинско-Заводский округ</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>26-021</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>МОУ Нерчинско-Заводская СОШ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>26-021-002</t>
         </is>
       </c>
     </row>
@@ -5455,9 +6038,24 @@
           <t>Оловяннинский округ</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>26-022</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>МБОУ Оловяннинская СОШ № 1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>26-022-001</t>
         </is>
       </c>
     </row>
@@ -5470,9 +6068,24 @@
           <t>Оловяннинский округ</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>26-022</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>МБОУ Оловяннинская СОШ № 235</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>26-022-002</t>
         </is>
       </c>
     </row>
@@ -5485,9 +6098,24 @@
           <t>Ононский округ</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>26-023</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>МБОУ 'Верхнецасучейская СОШ'</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>26-023-001</t>
         </is>
       </c>
     </row>
@@ -5500,9 +6128,24 @@
           <t>Ононский округ</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>26-023</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>МБОУ 'Нижнецасучейская СОШ'</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>26-023-002</t>
         </is>
       </c>
     </row>
@@ -5515,9 +6158,24 @@
           <t>Петровск-Забайкальский округ</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>26-024</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>МОУ Гимназия №1</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>26-024-001</t>
         </is>
       </c>
     </row>
@@ -5530,9 +6188,24 @@
           <t>Петровск-Забайкальский округ</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>26-024</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>МОУ средняя общеобразовательная школа с.Тарбагатай</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>26-024-002</t>
         </is>
       </c>
     </row>
@@ -5545,9 +6218,24 @@
           <t>Приаргунский округ</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>26-025</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>МБОУ Молодежнинская СОШ имени Л.С.Милоградова</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>26-025-001</t>
         </is>
       </c>
     </row>
@@ -5560,9 +6248,24 @@
           <t>Приаргунский округ</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>26-025</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>МБОУ Приаргунская средняя общеобразовательная школа</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>26-025-002</t>
         </is>
       </c>
     </row>
@@ -5575,9 +6278,24 @@
           <t>Сретенский район</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>26-026</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>МОУ 'Кокуйская СОШ № 2'</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>26-026-001</t>
         </is>
       </c>
     </row>
@@ -5590,9 +6308,24 @@
           <t>Сретенский район</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>26-026</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>МОУ 'Сретенская СОШ № 1'</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>26-026-002</t>
         </is>
       </c>
     </row>
@@ -5605,9 +6338,24 @@
           <t>Тунгиро-Олекминский район</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>26-027</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>МБОУ 'Тупикская средняя общеобразовательная школа'</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>26-027-001</t>
         </is>
       </c>
     </row>
@@ -5620,9 +6368,24 @@
           <t>Тунгокоченский округ</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>26-028</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>МБОУ ВУСОШ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>26-028-001</t>
         </is>
       </c>
     </row>
@@ -5635,9 +6398,24 @@
           <t>Улётовский район</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>26-029</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>МБОУ Улётовская СОШ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>26-029-001</t>
         </is>
       </c>
     </row>
@@ -5650,9 +6428,24 @@
           <t>Хилокский район</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>26-030</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>МБОУ СОШ № 10 г. Хилок</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>26-030-001</t>
         </is>
       </c>
     </row>
@@ -5665,9 +6458,24 @@
           <t>Хилокский район</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>26-030</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>МБОУ СОШ № 20 с.Линево-Озеро</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>26-030-002</t>
         </is>
       </c>
     </row>
@@ -5680,9 +6488,24 @@
           <t>Чернышевский округ</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>26-031</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>МОУ СОШ № 70</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>26-031-001</t>
         </is>
       </c>
     </row>
@@ -5695,9 +6518,24 @@
           <t>Чернышевский округ</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>26-031</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>МОУ СОШ № 78 пгт. Чернышевск</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>26-031-002</t>
         </is>
       </c>
     </row>
@@ -5710,9 +6548,24 @@
           <t>Читинский округ</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>26-032</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>МАОО 'СОШ №1' с. Смоленка</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>26-032-001</t>
         </is>
       </c>
     </row>
@@ -5725,9 +6578,24 @@
           <t>Читинский округ</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>26-032</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>МОУ СОШ с. Домна</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>26-032-002</t>
         </is>
       </c>
     </row>
@@ -5740,9 +6608,24 @@
           <t>Читинский округ</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>26-032</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>МОУ СОШ с. Засопка</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>26-032-003</t>
         </is>
       </c>
     </row>
@@ -5755,9 +6638,24 @@
           <t>Шелопугинский округ</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>26-033</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>МОУ Шелопугинская СОШ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>26-033-001</t>
         </is>
       </c>
     </row>
@@ -5770,9 +6668,24 @@
           <t>Шилкинский район</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>26-034</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>МОУ ПЕРВОМАЙСКАЯ СОШ №5</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>26-034-001</t>
         </is>
       </c>
     </row>
@@ -5785,9 +6698,24 @@
           <t>Шилкинский район</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>26-034</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>МОУ СОШ ИМ.Г.П.БОГОМЯГКОВО</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>26-034-002</t>
         </is>
       </c>
     </row>
@@ -5800,9 +6728,24 @@
           <t>Шилкинский район</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>26-034</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>МОУ ШИЛКИНСКАЯ СОШ №51</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>26-034-003</t>
         </is>
       </c>
     </row>
